--- a/模块一测试用例清单.xlsx
+++ b/模块一测试用例清单.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Information文档信息" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="Result">'Test Cases测试用例'!$N$2:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases测试用例'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases测试用例'!$A$1:$M$26</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" concurrentCalc="0"/>
 </workbook>
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\.mm\.dd"/>
     <numFmt numFmtId="165" formatCode="yy\.mm\.dd"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <name val="Arial"/>
       <charset val="134"/>
@@ -233,11 +233,6 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="38">
@@ -464,7 +459,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -782,21 +777,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -945,7 +925,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1112,10 +1092,6 @@
       <alignment horizontal="centerContinuous"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1253,7 +1229,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1396,13 +1372,13 @@
                 <formatCode>0.00%</formatCode>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>-1.42417682579469e-05</v>
+                  <v>-2.23801264477144e-05</v>
                 </pt>
                 <pt idx="1">
                   <v>0</v>
                 </pt>
                 <pt idx="2">
-                  <v>-2.03453832256384e-06</v>
+                  <v>-3.05183542468833e-06</v>
                 </pt>
                 <pt idx="3">
                   <v>0</v>
@@ -1462,7 +1438,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2874,7 +2850,7 @@
       </c>
       <c r="M2" s="13" t="inlineStr">
         <is>
-          <t>等价类</t>
+          <t>等价类划分法</t>
         </is>
       </c>
       <c r="N2" s="9" t="inlineStr">
@@ -2946,7 +2922,7 @@
       </c>
       <c r="M3" s="13" t="inlineStr">
         <is>
-          <t>边界值</t>
+          <t>边界值分析法</t>
         </is>
       </c>
       <c r="N3" s="9" t="inlineStr">
@@ -3018,7 +2994,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>边界值</t>
+          <t>边界值分析法</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
@@ -3090,7 +3066,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>边界值</t>
+          <t>边界值分析法</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
@@ -3162,7 +3138,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>边界值</t>
+          <t>边界值分析法</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3205,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>等价类</t>
+          <t>场景法</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3272,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>边界值</t>
+          <t>边界值分析法</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3406,7 @@
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>异常场景</t>
+          <t>错误推测法</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3473,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>等价类</t>
+          <t>场景法</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3540,7 @@
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>异常场景</t>
+          <t>等价类划分法</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3741,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>异常场景</t>
+          <t>错误推测法</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3808,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>等价类</t>
+          <t>等价类划分法</t>
         </is>
       </c>
     </row>
@@ -3899,610 +3875,610 @@
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>异常场景</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-001</t>
-        </is>
-      </c>
-      <c r="B18" s="60" t="inlineStr">
+          <t>错误推测法</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-001</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>cache.py基础功能</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>正常初始化两层缓存</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F18" s="60" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G18" s="60" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Python环境及依赖已安装</t>
         </is>
       </c>
-      <c r="H18" s="60" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>layer_num=2，model_type='llama'，CPU</t>
         </is>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>创建MMSepCache对象</t>
         </is>
       </c>
-      <c r="J18" s="60" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>对象创建成功，layer_num=2</t>
         </is>
       </c>
-      <c r="K18" s="60" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>验证对象属性及空缓存状态</t>
         </is>
       </c>
-      <c r="L18" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M18" s="60" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-002</t>
-        </is>
-      </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>等价类划分法</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-002</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>cache.py参数校验</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>缺少layer_num时拒绝初始化</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G19" s="60" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>已导入MMSepCache</t>
         </is>
       </c>
-      <c r="H19" s="60" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>不传layer_num</t>
         </is>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>创建MMSepCache(model_type='llama')</t>
         </is>
       </c>
-      <c r="J19" s="60" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>抛出AssertionError</t>
         </is>
       </c>
-      <c r="K19" s="60" t="inlineStr">
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>实际抛出AssertionError</t>
         </is>
       </c>
-      <c r="L19" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M19" s="60" t="inlineStr">
-        <is>
-          <t>pytest.raises</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-003</t>
-        </is>
-      </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>边界值分析法</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28.5" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-003</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>cache.py参数校验</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>分层参数长度错误</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G20" s="60" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>layer_num=2</t>
         </is>
       </c>
-      <c r="H20" s="60" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>local_size=[2]</t>
         </is>
       </c>
-      <c r="I20" s="60" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>创建缓存对象</t>
         </is>
       </c>
-      <c r="J20" s="60" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>抛出AssertionError</t>
         </is>
       </c>
-      <c r="K20" s="60" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>实际抛出AssertionError</t>
         </is>
       </c>
-      <c r="L20" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M20" s="60" t="inlineStr">
-        <is>
-          <t>pytest.raises</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-004</t>
-        </is>
-      </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>边界值分析法</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-004</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>cache.py缓存写入</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>预填充写入KV和token</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F21" s="60" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G21" s="60" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>缓存对象已创建</t>
         </is>
       </c>
-      <c r="H21" s="60" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>key/value形状[1,1,3,2]，input_ids=[[10,11,12]]</t>
         </is>
       </c>
-      <c r="I21" s="60" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>调用update(PREFILLING_FLAG=True)</t>
         </is>
       </c>
-      <c r="J21" s="60" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>KV与输入数据一致，缓存长度为3</t>
         </is>
       </c>
-      <c r="K21" s="60" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>KV、token及长度均符合预期</t>
         </is>
       </c>
-      <c r="L21" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M21" s="60" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-005</t>
-        </is>
-      </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-005</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>cache.py多层缓存</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>第二层独立保存预填充数据</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E22" s="60" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F22" s="60" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G22" s="60" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>两层缓存已创建</t>
         </is>
       </c>
-      <c r="H22" s="60" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>layer_idx=0和1分别写入长度2的KV</t>
         </is>
       </c>
-      <c r="I22" s="60" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>连续调用两次update</t>
         </is>
       </c>
-      <c r="J22" s="60" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>两层均有缓存，batch_size=1</t>
         </is>
       </c>
-      <c r="K22" s="60" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>两层缓存均写入成功</t>
         </is>
       </c>
-      <c r="L22" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M22" s="60" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-006</t>
-        </is>
-      </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43.5" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-006</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>cache.py缓存追加</t>
         </is>
       </c>
-      <c r="C23" s="60" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>解码阶段追加一个token</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E23" s="60" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F23" s="60" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G23" s="60" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>第0层已有3个token</t>
         </is>
       </c>
-      <c r="H23" s="60" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>追加长度1的KV和token 4</t>
         </is>
       </c>
-      <c r="I23" s="60" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>调用update(PREFILLING_FLAG=False)</t>
         </is>
       </c>
-      <c r="J23" s="60" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>缓存长度由3增加到4</t>
         </is>
       </c>
-      <c r="K23" s="60" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>缓存长度和token序列正确</t>
         </is>
       </c>
-      <c r="L23" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M23" s="60" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-007</t>
-        </is>
-      </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="43.5" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-007</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>cache.py位置偏移</t>
         </is>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>统计padding token位置偏移</t>
         </is>
       </c>
-      <c r="D24" s="60" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E24" s="60" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F24" s="60" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G24" s="60" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>llama模型缓存已创建</t>
         </is>
       </c>
-      <c r="H24" s="60" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>token_ids=[[128009,128009,10]]</t>
         </is>
       </c>
-      <c r="I24" s="60" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>预填充后调用get_initial_pos_offset(0)</t>
         </is>
       </c>
-      <c r="J24" s="60" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>返回偏移量2</t>
         </is>
       </c>
-      <c r="K24" s="60" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>返回值为2</t>
         </is>
       </c>
-      <c r="L24" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M24" s="60" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-008</t>
-        </is>
-      </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>边界值分析法</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28.5" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-008</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>cache.py异常处理</t>
         </is>
       </c>
-      <c r="C25" s="60" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>空缓存获取batch size</t>
         </is>
       </c>
-      <c r="D25" s="60" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="E25" s="60" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F25" s="60" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G25" s="60" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>缓存对象已创建且未写入数据</t>
         </is>
       </c>
-      <c r="H25" s="60" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="I25" s="60" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>调用get_batch_size()</t>
         </is>
       </c>
-      <c r="J25" s="60" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>抛出AssertionError</t>
         </is>
       </c>
-      <c r="K25" s="60" t="inlineStr">
+      <c r="K25" s="14" t="inlineStr">
         <is>
           <t>实际抛出AssertionError</t>
         </is>
       </c>
-      <c r="L25" s="60" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M25" s="60" t="inlineStr">
-        <is>
-          <t>pytest.raises</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="60" t="inlineStr">
-        <is>
-          <t>CACHE-B-009</t>
-        </is>
-      </c>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>错误推测法</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>MMSep-CACHE-009</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>cache.py缓存读取</t>
         </is>
       </c>
-      <c r="C26" s="60" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>读取指定层KV缓存</t>
         </is>
       </c>
-      <c r="D26" s="60" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E26" s="60" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F26" s="60" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G26" s="60" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>第0层已写入KV</t>
         </is>
       </c>
-      <c r="H26" s="60" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>layer_idx=0</t>
         </is>
       </c>
-      <c r="I26" s="60" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>调用get_kv_pair(0)</t>
         </is>
       </c>
-      <c r="J26" s="60" t="inlineStr">
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>返回与写入时一致的key/value</t>
         </is>
       </c>
-      <c r="K26" s="60" t="inlineStr">
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>原始 cache.py 调用 get_kv_pair(0) 时抛出 RuntimeError：The KV for layer:0 have not been set.</t>
         </is>
       </c>
-      <c r="L26" s="60" t="inlineStr">
-        <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="M26" s="60" t="inlineStr">
-        <is>
-          <t>缺陷：get_kv_pair 判断条件写反。使用 cache_fixed.py 修复后该用例通过。</t>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>错误推测法</t>
         </is>
       </c>
     </row>
@@ -42076,10 +42052,10 @@
       <c r="L12389" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M26"/>
   <dataValidations count="3">
     <dataValidation sqref="K2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Warning" error="Invalide Data"/>
-    <dataValidation sqref="L2:L12389" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L16 L17:L25 L26:L12389" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Result</formula1>
     </dataValidation>
     <dataValidation sqref="L12390:L65536" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">

--- a/模块一测试用例清单.xlsx
+++ b/模块一测试用例清单.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="266">
   <si>
     <t>Test  Case Form 测试用例表单</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Project ID 项目ID</t>
   </si>
   <si>
-    <t>MMSep-AE</t>
+    <t>MMSep-AE/CACHE</t>
   </si>
   <si>
     <t>Prepared by 拟制</t>
@@ -76,13 +76,13 @@
     <t>Date 日期</t>
   </si>
   <si>
-    <t>2026.09.11</t>
+    <t>2026.09.13</t>
   </si>
   <si>
     <t>Reviewed by 评审人</t>
   </si>
   <si>
-    <t>16</t>
+    <t>待填写</t>
   </si>
   <si>
     <t>Approved by 批准</t>
@@ -94,7 +94,7 @@
     <t>Introduction 概述</t>
   </si>
   <si>
-    <t>针对 auto_eval.py 的单元测试，使用本地 JSONL 数据和 Mock Ark 客户端，不访问真实 API。</t>
+    <t>针对 MMSep 项目中的 auto_eval.py 与 cache.py 进行单元测试。auto_eval.py 使用本地 JSONL 数据和 Mock Ark 客户端，不访问真实 API；cache.py 重点验证缓存初始化、写入、追加、位置偏移、异常处理与 KV 缓存读取功能。</t>
   </si>
   <si>
     <t>Revision Record 修订记录</t>
@@ -115,16 +115,10 @@
     <t>Author 作者</t>
   </si>
   <si>
-    <t>1.00</t>
+    <t>1.01</t>
   </si>
   <si>
-    <t>初稿</t>
-  </si>
-  <si>
-    <t>完成 auto_eval.py 测试用例清单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汪嘉楠 </t>
+    <t>—</t>
   </si>
   <si>
     <t>Distribution LIST 分发记录</t>
@@ -142,16 +136,22 @@
     <t>&lt;T.M.B&amp;C.P.M&gt;</t>
   </si>
   <si>
+    <t>2026.09.11</t>
+  </si>
+  <si>
     <t>&lt;Project Manager&gt;</t>
   </si>
   <si>
-    <t>yyyy.mm.dd</t>
+    <t>待分发</t>
   </si>
   <si>
     <t>&lt;Team members&gt;</t>
   </si>
   <si>
     <t>&lt;Customer Representative&gt;</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>&lt;Others&gt;</t>
@@ -206,12 +206,20 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="1200"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Pre-condition </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="1200"/>
+        <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -451,11 +459,17 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="1100"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>实际抛出</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -629,9 +643,6 @@
     <t>正常初始化两层缓存</t>
   </si>
   <si>
-    <t>高</t>
-  </si>
-  <si>
     <t>否</t>
   </si>
   <si>
@@ -657,9 +668,6 @@
   </si>
   <si>
     <t>缺少layer_num时拒绝初始化</t>
-  </si>
-  <si>
-    <t>中</t>
   </si>
   <si>
     <t>已导入MMSepCache；不传layer_num。</t>
@@ -797,9 +805,6 @@
     <t>空缓存获取batch size</t>
   </si>
   <si>
-    <t>低</t>
-  </si>
-  <si>
     <t>缓存已创建，尚未写入数据。</t>
   </si>
   <si>
@@ -831,11 +836,17 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="1100"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>原始</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -844,7 +855,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -853,7 +864,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -862,7 +873,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -871,7 +882,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -880,7 +891,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -889,7 +900,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -944,7 +955,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\.mm\.dd"/>
     <numFmt numFmtId="177" formatCode="yy\.mm\.dd"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
@@ -1138,7 +1149,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="1200"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="1100"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="1100"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -1805,7 +1829,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1870,11 +1894,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2464,7 +2491,7 @@
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
-        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{6fd21c26-6267-4452-a2fd-5a02673cea63}"/>
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{a62aa858-b98b-4a71-bd10-8649aa62bb0a}"/>
       </c:ext>
     </c:extLst>
   </c:chart>
@@ -2947,14 +2974,14 @@
         <v>20</v>
       </c>
       <c r="C16" s="27"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="21"/>
     </row>
     <row r="17" ht="3.9" customHeight="1" spans="2:12">
@@ -2985,54 +3012,52 @@
       <c r="L18" s="21"/>
     </row>
     <row r="19" ht="48" customHeight="1" spans="2:12">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="28" t="s">
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="29" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="21"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="2:12">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="32" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>29</v>
-      </c>
+      <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
       <c r="I20" s="22"/>
       <c r="J20" s="22"/>
       <c r="K20" s="23" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="L20" s="21"/>
     </row>
     <row r="21" ht="16.2" customHeight="1" spans="2:12">
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -3044,8 +3069,8 @@
       <c r="L21" s="21"/>
     </row>
     <row r="22" ht="16.2" customHeight="1" spans="2:12">
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -3057,8 +3082,8 @@
       <c r="L22" s="21"/>
     </row>
     <row r="23" ht="16.2" customHeight="1" spans="2:12">
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -3070,9 +3095,9 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" ht="16.2" customHeight="1" spans="2:12">
-      <c r="B24" s="30"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="33"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -3083,8 +3108,8 @@
       <c r="L24" s="21"/>
     </row>
     <row r="25" ht="16.2" customHeight="1" spans="2:12">
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="32"/>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -3109,7 +3134,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1" spans="2:12">
       <c r="B27" s="20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -3123,11 +3148,11 @@
       <c r="L27" s="21"/>
     </row>
     <row r="28" ht="16.2" customHeight="1" spans="2:12">
-      <c r="B28" s="33" t="s">
-        <v>32</v>
+      <c r="B28" s="34" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
@@ -3136,7 +3161,7 @@
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
       <c r="J28" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K28" s="20"/>
       <c r="L28" s="21"/>
@@ -3146,20 +3171,20 @@
         <v>1</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
-      <c r="F29" s="34" t="s">
+      <c r="F29" s="35" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="I29" s="22"/>
-      <c r="J29" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" s="30"/>
+      <c r="J29" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="31"/>
       <c r="L29" s="21"/>
     </row>
     <row r="30" spans="2:12">
@@ -3167,7 +3192,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -3175,10 +3200,10 @@
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="I30" s="22"/>
-      <c r="J30" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="K30" s="30"/>
+      <c r="J30" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="K30" s="31"/>
       <c r="L30" s="21"/>
     </row>
     <row r="31" spans="2:12">
@@ -3186,7 +3211,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -3194,10 +3219,10 @@
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="I31" s="22"/>
-      <c r="J31" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="K31" s="30"/>
+      <c r="J31" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="31"/>
       <c r="L31" s="21"/>
     </row>
     <row r="32" spans="2:12">
@@ -3205,7 +3230,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -3213,130 +3238,130 @@
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
-      <c r="J32" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="K32" s="30"/>
+      <c r="J32" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="31"/>
       <c r="L32" s="21"/>
     </row>
     <row r="33" spans="2:11">
-      <c r="B33" s="35">
+      <c r="B33" s="36">
         <v>5</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="K33" s="38"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="39"/>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="2:11">
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="44"/>
     </row>
     <row r="38" ht="16.2" customHeight="1" spans="2:11">
-      <c r="B38" s="44" t="s">
+      <c r="B38" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="45">
+      <c r="C38" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
         <v>22</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D38" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="46">
+      <c r="E38" s="47">
         <f>IF(E13=0,0,C38/E13)</f>
         <v>0.88</v>
       </c>
     </row>
     <row r="39" ht="16.2" customHeight="1" spans="2:11">
-      <c r="B39" s="44" t="s">
+      <c r="B39" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="45">
+      <c r="C39" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=POK"))</f>
         <v>0</v>
       </c>
-      <c r="D39" s="44" t="s">
+      <c r="D39" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="46">
+      <c r="E39" s="47">
         <f>IF(E13=0,0,C39/E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" ht="16.2" customHeight="1" spans="2:11">
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="45">
+      <c r="C40" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
         <v>3</v>
       </c>
-      <c r="D40" s="44" t="s">
+      <c r="D40" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="46">
+      <c r="E40" s="47">
         <f>IF(E13=0,0,C40/E13)</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="41" ht="16.2" customHeight="1" spans="2:11">
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="49">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NT"))</f>
         <v>0</v>
       </c>
-      <c r="D41" s="47" t="s">
+      <c r="D41" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="49">
+      <c r="E41" s="50">
         <f>IF(E13=0,0,C41/E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="3" customHeight="1" spans="2:11">
-      <c r="B42" s="50"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="53"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="54"/>
     </row>
     <row r="43" ht="16.2" customHeight="1" spans="2:11">
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="55">
+      <c r="C43" s="56">
         <f>E13</f>
         <v>25</v>
       </c>
-      <c r="D43" s="56"/>
-      <c r="E43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4219,28 +4244,28 @@
         <v>190</v>
       </c>
       <c r="D18" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="F18" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="H18" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="I18" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="J18" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="K18" s="13" t="s">
         <v>196</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>197</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>74</v>
@@ -4251,37 +4276,37 @@
     </row>
     <row r="19" ht="43.5" customHeight="1" spans="1:13">
       <c r="A19" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="I19" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="J19" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="K19" s="13" t="s">
         <v>204</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>206</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>74</v>
@@ -4292,37 +4317,37 @@
     </row>
     <row r="20" ht="28.5" customHeight="1" spans="1:13">
       <c r="A20" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="H20" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G20" s="13" t="s">
+      <c r="I20" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="H20" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>211</v>
-      </c>
       <c r="J20" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>74</v>
@@ -4333,37 +4358,37 @@
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:13">
       <c r="A21" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="H21" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="I21" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="J21" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="K21" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>219</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>74</v>
@@ -4374,37 +4399,37 @@
     </row>
     <row r="22" ht="45" customHeight="1" spans="1:13">
       <c r="A22" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="H22" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G22" s="13" t="s">
+      <c r="I22" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="J22" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="K22" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>227</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>74</v>
@@ -4415,37 +4440,37 @@
     </row>
     <row r="23" ht="43.5" customHeight="1" spans="1:13">
       <c r="A23" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G23" s="13" t="s">
+      <c r="I23" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="J23" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="K23" s="13" t="s">
         <v>233</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>235</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>74</v>
@@ -4456,37 +4481,37 @@
     </row>
     <row r="24" ht="43.5" customHeight="1" spans="1:13">
       <c r="A24" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="D24" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="H24" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G24" s="13" t="s">
+      <c r="I24" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="J24" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="K24" s="13" t="s">
         <v>241</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>243</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>74</v>
@@ -4497,37 +4522,37 @@
     </row>
     <row r="25" ht="28.5" customHeight="1" spans="1:13">
       <c r="A25" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="I25" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>250</v>
-      </c>
       <c r="J25" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L25" s="13" t="s">
         <v>74</v>
@@ -4538,37 +4563,37 @@
     </row>
     <row r="26" ht="120" customHeight="1" spans="1:13">
       <c r="A26" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="H26" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="I26" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="J26" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="K26" s="15" t="s">
         <v>255</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L26" s="13" t="s">
         <v>91</v>
@@ -42174,7 +42199,7 @@
   <sheetData>
     <row r="1" ht="16.2" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42184,7 +42209,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42193,7 +42218,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42202,7 +42227,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42211,7 +42236,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42220,7 +42245,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42229,7 +42254,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42238,7 +42263,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42247,7 +42272,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42256,7 +42281,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
